--- a/backend/examples/excel/比赛建包模板.xlsx
+++ b/backend/examples/excel/比赛建包模板.xlsx
@@ -89,7 +89,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. 第一行是表头，列名不要改（就是建包库的参数名）；列顺序随意，多余列会被拒绝（公司表除外）。</t>
+          <t xml:space="preserve">2. 第一行是中文表头，**不要改**；需要对照代码时看最后一栏「参数名」。列顺序随意。</t>
         </is>
       </c>
     </row>
@@ -110,7 +110,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. 建包命令：python examples/excel/build_from_sheets.py 本文件.xlsx --competition &lt;比赛id&gt; [--dry-run]</t>
+          <t xml:space="preserve">5. 建包命令：python examples/excel/build_from_sheets.py 本文件.xlsx --create-competition [--dry-run]</t>
         </is>
       </c>
     </row>
@@ -121,62 +121,47 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">表清单</t>
-        </is>
-      </c>
-    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7. 英文参数名同样可用（老文件兼容）；中文表头与参数名指向同一列，不要同时写两列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">表名</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">分组</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">列（* = 必填）</t>
+          <t xml:space="preserve">表清单</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛</t>
+          <t xml:space="preserve">表名</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">competition</t>
+          <t xml:space="preserve">分组</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛本身：名称、状态、地图背景图（整表一行）</t>
+          <t xml:space="preserve">用途</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、status、map_background_url、map_background_width、map_background_height</t>
+          <t xml:space="preserve">列（* = 必填）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">财年</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -186,41 +171,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">财年：新建 / 由非 ACTIVE 改为 ACTIVE 会触发 FY_START 定时器</t>
+          <t xml:space="preserve">比赛本身：名称、状态、地图背景图（整表一行）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">year*、status</t>
+          <t xml:space="preserve">比赛名称*、状态、地图背景图地址、背景图宽、背景图高</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
+          <t xml:space="preserve">财年</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry</t>
+          <t xml:space="preserve">competition</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局资源：行业口径（按 code 跨比赛复用，不要给不同行业用同一个 code）</t>
+          <t xml:space="preserve">财年：新建 / 由非 ACTIVE 改为 ACTIVE 会触发 FY_START 定时器</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">code*、name*、description、icon</t>
+          <t xml:space="preserve">年份*、状态</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -230,41 +215,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局资源：产业下的字段（合同、图表、股票都按 field_key 绑定）</t>
+          <t xml:space="preserve">全局资源：行业口径（按 code 跨比赛复用，不要给不同行业用同一个 code）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry_type*、name*、field_key*、field_type、default_value、is_calculated、graph、timer_enabled、timer_trigger、timer_value、sort_order、visible、config</t>
+          <t xml:space="preserve">编码*、产业名称*、说明、图标</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">company</t>
+          <t xml:space="preserve">industry</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛内区域（区域总览、总览卡片按它聚合）</t>
+          <t xml:space="preserve">全局资源：产业下的字段（合同、图表、股票都按 field_key 绑定）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、description</t>
+          <t xml:space="preserve">所属产业*、字段名称*、字段键*、字段类型、默认值、是否计算字段、计算图、启用财年定时器、定时器时机、定时器写入值、排序、是否展示、类型配置</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司</t>
+          <t xml:space="preserve">区域</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -274,19 +259,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">参赛公司；**额外列会被当作该公司的产业字段初始值**（列名 = field_key）</t>
+          <t xml:space="preserve">比赛内区域（区域总览、总览卡片按它聚合）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、industry_type*、region、status、（额外列：列名 = field_key，填公司的产业字段初始值）</t>
+          <t xml:space="preserve">区域名称*、说明</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司字段值</t>
+          <t xml:space="preserve">公司</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -296,41 +281,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">单独维护公司字段值（与公司表二选一或并用，后写覆盖先写）</t>
+          <t xml:space="preserve">参赛公司；**额外列会被当作该公司的产业字段初始值**（列名 = field_key）</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">company*、field_key*、value</t>
+          <t xml:space="preserve">公司名称*、所属产业*、所属区域、状态、（额外列：列名写字段键或字段显示名，填公司的产业字段初始值）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点类型</t>
+          <t xml:space="preserve">公司字段值</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">geo</t>
+          <t xml:space="preserve">company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点分类（矿区 / 港口 / 城市 …）</t>
+          <t xml:space="preserve">单独维护公司字段值（与公司表二选一或并用，后写覆盖先写）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、description、color</t>
+          <t xml:space="preserve">公司名称*、字段键*、值</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">地图节点类型</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -340,19 +325,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">道路类型（公路 / 铁路 / 航运）；载具按它判断可通行</t>
+          <t xml:space="preserve">地图节点分类（矿区 / 港口 / 城市 …）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、description、color</t>
+          <t xml:space="preserve">类型名称*、说明、颜色</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -362,19 +347,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点（region 是文本列，不是外键）</t>
+          <t xml:space="preserve">道路类型（公路 / 铁路 / 航运）；载具按它判断可通行</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、node_type*、region、x、y</t>
+          <t xml:space="preserve">类型名称*、说明、颜色</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图连线</t>
+          <t xml:space="preserve">地图节点</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -384,41 +369,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点之间的连线；同一对「起点+终点」只能有一条（反向算另一条）</t>
+          <t xml:space="preserve">地图节点（region 是文本列，不是外键）</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_node*、to_node*、distance*、path_type*</t>
+          <t xml:space="preserve">节点名称*、节点类型*、所属区域、X坐标、Y坐标</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">地图连线</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">geo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料（载具必须绑定燃料，外键 PROTECT）</t>
+          <t xml:space="preserve">节点之间的连线；同一对「起点+终点」只能有一条（反向算另一条）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、price_per_liter</t>
+          <t xml:space="preserve">起点节点*、终点节点*、距离(公里)*、路径类型*</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -428,19 +413,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料（地点价按地图节点名写；运输与运费计算都依赖它）</t>
+          <t xml:space="preserve">燃料（载具必须绑定燃料，外键 PROTECT）</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、origin、carbon_emission_coefficient、type、node_prices</t>
+          <t xml:space="preserve">燃料名称*、每升单价</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技</t>
+          <t xml:space="preserve">原料</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -450,19 +435,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技节点（零件 / 产品按它设前置）</t>
+          <t xml:space="preserve">原料（地点价按地图节点名写；运输与运费计算都依赖它）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、tier、research_cost、description、prerequisites</t>
+          <t xml:space="preserve">原料名称*、产地、碳排系数、类型、地点价</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线</t>
+          <t xml:space="preserve">科技</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -472,19 +457,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线（产能与用工人数）</t>
+          <t xml:space="preserve">科技节点（零件 / 产品按它设前置）</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、price、labor_count、max_per_year</t>
+          <t xml:space="preserve">科技名称*、层级、研发费用、说明、前置科技</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建</t>
+          <t xml:space="preserve">生产线</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -494,19 +479,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建及其 6 项加成（合同可按清单聚合这些属性）</t>
+          <t xml:space="preserve">生产线（产能与用工人数）</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、footprint、price、activation_price、employment_rate_bonus、population_bonus、high_quality_population_bonus、happiness_index_bonus、per_capita_income_bonus、carbon_reduction_bonus</t>
+          <t xml:space="preserve">生产线名称*、单价、用工人数、年产能</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库</t>
+          <t xml:space="preserve">基建</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -516,19 +501,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库（MATERIAL / PART / PRODUCT / FUEL 四种建议都覆盖）</t>
+          <t xml:space="preserve">基建及其 6 项加成（合同可按清单聚合这些属性）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、type*、capacity、price</t>
+          <t xml:space="preserve">基建名称*、占地面积、单价、启用费用、就业率加成、人口加成、高素质人口加成、幸福度加成、人均收益加成、减碳加成</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件</t>
+          <t xml:space="preserve">仓库</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -538,19 +523,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件：原料配比 + 科技前置（配比只能引用原料）</t>
+          <t xml:space="preserve">仓库（MATERIAL / PART / PRODUCT / FUEL 四种建议都覆盖）</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、materials、tech</t>
+          <t xml:space="preserve">仓库名称*、仓库种类*、容量、单价</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品</t>
+          <t xml:space="preserve">零件</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -560,19 +545,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品：零件配比 + 科技前置（配比只能引用零件）</t>
+          <t xml:space="preserve">零件：原料配比 + 科技前置（配比只能引用原料）</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、parts、tech</t>
+          <t xml:space="preserve">零件名称*、原料配比、所需科技</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具</t>
+          <t xml:space="preserve">产品</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -582,63 +567,63 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具：绑定燃料 + 可通行路径类型（缺路径类型会导致运输校验失败）</t>
+          <t xml:space="preserve">产品：零件配比 + 科技前置（配比只能引用零件）</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">name*、fuel*、path_types、fuel_consumption_per_km、max_cargo、price、carbon_emission</t>
+          <t xml:space="preserve">产品名称*、零件配比、所需科技</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费者需求</t>
+          <t xml:space="preserve">载具</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">tech</t>
+          <t xml:space="preserve">supply</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域消费者需求（导入按「区域+产品+数量」去重，改数量 = 新增一条）</t>
+          <t xml:space="preserve">载具：绑定燃料 + 可通行路径类型（缺路径类型会导致运输校验失败）</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">region*、product*、quantity*、note</t>
+          <t xml:space="preserve">载具名称*、燃料*、可通行路径类型、每公里油耗、载货量、单价、碳排系数</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域总览卡片</t>
+          <t xml:space="preserve">消费者需求</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">market</t>
+          <t xml:space="preserve">tech</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域总览卡片（industryFieldId 由建包库自动回填，见文档两遍导入）</t>
+          <t xml:space="preserve">区域消费者需求（导入按「区域+产品+数量」去重，改数量 = 新增一条）</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">region*、company*、field_key*、display_name、zone、card_id</t>
+          <t xml:space="preserve">区域名称*、产品名称*、需求量*、备注</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">合同类型</t>
+          <t xml:space="preserve">区域总览卡片</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -648,19 +633,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局资源：合同模板。四份 JSON 可写 JSON，也可用 `script` 列指向合同类型代码化脚本</t>
+          <t xml:space="preserve">区域总览卡片（industryFieldId 由建包库自动回填，见文档两遍导入）</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">key*、name*、description、script、party_roles、input_schema、effects、conditions、enabled</t>
+          <t xml:space="preserve">区域名称*、公司名称*、字段键*、卡片标题、分区标记、卡片ID</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">合同实例</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -670,19 +655,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛内的预置合同（保持 DRAFT 不落账）。名称缺省取合同类型名，故每种类型只预置一份</t>
+          <t xml:space="preserve">全局资源：合同模板。四份 JSON 可写 JSON，也可用 `script` 列指向合同类型代码化脚本</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">contract_type*、name、parties、inputs、status</t>
+          <t xml:space="preserve">类型标识*、合同名称*、说明、脚本路径、参与方、输入项定义、效果定义、前置检查、是否启用</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">消息</t>
+          <t xml:space="preserve">合同实例</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -692,126 +677,3139 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛内消息（导入不做判重：重复导入会多建，注意去重）</t>
+          <t xml:space="preserve">比赛内的预置合同（保持 DRAFT 不落账）。名称缺省取合同类型名，故每种类型只预置一份</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">title*、content、to_all、to_users、sender</t>
+          <t xml:space="preserve">合同类型标识*、合同名称、参与方、输入项、状态</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t xml:space="preserve">消息</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">比赛内消息（导入不做判重：重复导入会多建，注意去重）</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标题*、正文、是否发给全体、指定收件人、发布者</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t xml:space="preserve">账号</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t xml:space="preserve">access</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve">参赛账号与四套公司范围（范围为空 = 登录后什么都看不到）</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">username*、role、display_name、company_scopes、view_company_scopes、contract_view_company_scopes、stock_company_scopes、permissions、is_active</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">列类型说明</t>
-        </is>
-      </c>
-    </row>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用户名*、角色、显示名、公司管理范围、查看范围、合同查看范围、股票范围、权限键、是否启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">表头 ↔ 参数名对照</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">表名</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">中文表头</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参数名</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">类型</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必填</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">bool</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">是/否</t>
+          <t xml:space="preserve">比赛名称</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">list</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">map</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
+          <t xml:space="preserve">地图背景图地址</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">map_background_url</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairs</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">键值（key=value，分号分隔）</t>
+          <t xml:space="preserve">背景图宽</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">map_background_width</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">json</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t xml:space="preserve">背景图高</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">map_background_height</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">财年</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">年份</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">year</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">财年</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业类型</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">编码</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">code</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业类型</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业名称</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业类型</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业类型</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">图标</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所属产业</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">industry_type</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字段名称</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字段键</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">field_key</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字段类型</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">field_type</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认值</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default_value</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否计算字段</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is_calculated</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是/否</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">计算图</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">graph</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t xml:space="preserve">JSON 文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">启用财年定时器</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timer_enabled</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是/否</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定时器时机</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timer_trigger</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定时器写入值</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timer_value</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">排序</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sort_order</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否展示</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">visible</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是/否</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产业字段</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">类型配置</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">config</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域名称</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司名称</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所属产业</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">industry_type</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所属区域</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">region</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司字段值</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司名称</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">company</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司字段值</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字段键</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">field_key</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司字段值</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">值</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图节点类型</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">类型名称</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图节点类型</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图节点类型</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">颜色</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">color</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">路径类型</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">类型名称</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">路径类型</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">路径类型</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">颜色</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">color</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图节点</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节点名称</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图节点</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节点类型</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node_type</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图节点</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所属区域</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">region</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图节点</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X坐标</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图节点</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y坐标</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图连线</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起点节点</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from_node</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图连线</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">终点节点</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to_node</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图连线</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">距离(公里)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">distance</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地图连线</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">路径类型</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">path_type</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燃料</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燃料名称</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燃料</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每升单价</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price_per_liter</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原料</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原料名称</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原料</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产地</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">origin</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原料</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碳排系数</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carbon_emission_coefficient</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原料</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">类型</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原料</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地点价</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node_prices</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科技</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科技名称</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科技</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">层级</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tier</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科技</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">研发费用</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">research_cost</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科技</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">科技</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前置科技</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prerequisites</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表（分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生产线</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生产线名称</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生产线</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单价</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生产线</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用工人数</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labor_count</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生产线</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">年产能</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">max_per_year</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建名称</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">占地面积</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">footprint</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单价</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">启用费用</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">activation_price</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">就业率加成</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">employment_rate_bonus</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人口加成</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">population_bonus</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高素质人口加成</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">high_quality_population_bonus</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幸福度加成</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">happiness_index_bonus</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人均收益加成</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_capita_income_bonus</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基建</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">减碳加成</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carbon_reduction_bonus</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仓库</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仓库名称</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仓库</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仓库种类</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仓库</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">容量</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">capacity</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仓库</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单价</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">零件</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">零件名称</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">零件</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原料配比</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">materials</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">零件</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所需科技</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tech</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表（分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产品</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产品名称</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产品</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">零件配比</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parts</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产品</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所需科技</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tech</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表（分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载具</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载具名称</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载具</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燃料</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuel</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载具</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可通行路径类型</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">path_types</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表（分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载具</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每公里油耗</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuel_consumption_per_km</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载具</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载货量</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">max_cargo</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载具</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单价</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载具</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碳排系数</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carbon_emission</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消费者需求</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域名称</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">region</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消费者需求</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产品名称</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">product</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消费者需求</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">需求量</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quantity</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消费者需求</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">备注</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域总览卡片</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域名称</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">region</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域总览卡片</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司名称</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">company</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域总览卡片</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字段键</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">field_key</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域总览卡片</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卡片标题</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">display_name</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域总览卡片</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分区标记</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zone</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域总览卡片</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卡片ID</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">card_id</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">类型标识</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同名称</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">脚本路径</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">script</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参与方</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">party_roles</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JSON 文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">输入项定义</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">input_schema</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JSON 文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">效果定义</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effects</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JSON 文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前置检查</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">conditions</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JSON 文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否启用</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enabled</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是/否</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同实例</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型标识</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contract_type</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同实例</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同名称</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同实例</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参与方</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parties</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同实例</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">输入项</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inputs</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">键值（key=value，分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同实例</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状态</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消息</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">标题</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消息</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正文</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">content</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消息</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否发给全体</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to_all</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是/否</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消息</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">指定收件人</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to_users</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表（分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消息</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发布者</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sender</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">账号</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用户名</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">username</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">账号</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">角色</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">role</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">账号</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">显示名</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">display_name</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">账号</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公司管理范围</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">company_scopes</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表（分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">账号</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">查看范围</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">view_company_scopes</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表（分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">账号</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同查看范围</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contract_view_company_scopes</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表（分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">账号</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">股票范围</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stock_company_scopes</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表（分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">账号</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限键</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">permissions</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">列表（分号分隔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">账号</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否启用</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is_active</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是/否</t>
         </is>
       </c>
     </row>
@@ -825,17 +3823,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">color</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
     </row>
@@ -869,27 +3867,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">节点名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node_type</t>
+          <t xml:space="preserve">节点类型</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">所属区域</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">x</t>
+          <t xml:space="preserve">X坐标</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">y</t>
+          <t xml:space="preserve">Y坐标</t>
         </is>
       </c>
     </row>
@@ -933,22 +3931,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_node</t>
+          <t xml:space="preserve">起点节点</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_node</t>
+          <t xml:space="preserve">终点节点</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">distance</t>
+          <t xml:space="preserve">距离(公里)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">path_type</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
     </row>
@@ -987,12 +3985,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">燃料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">price_per_liter</t>
+          <t xml:space="preserve">每升单价</t>
         </is>
       </c>
     </row>
@@ -1021,27 +4019,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">原料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">origin</t>
+          <t xml:space="preserve">产地</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_emission_coefficient</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">类型</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node_prices</t>
+          <t xml:space="preserve">地点价</t>
         </is>
       </c>
     </row>
@@ -1085,27 +4083,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">科技名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">层级</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">research_cost</t>
+          <t xml:space="preserve">研发费用</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prerequisites</t>
+          <t xml:space="preserve">前置科技</t>
         </is>
       </c>
     </row>
@@ -1144,22 +4142,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">生产线名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">labor_count</t>
+          <t xml:space="preserve">用工人数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_per_year</t>
+          <t xml:space="preserve">年产能</t>
         </is>
       </c>
     </row>
@@ -1198,52 +4196,52 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">基建名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">footprint</t>
+          <t xml:space="preserve">占地面积</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">activation_price</t>
+          <t xml:space="preserve">启用费用</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">employment_rate_bonus</t>
+          <t xml:space="preserve">就业率加成</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">population_bonus</t>
+          <t xml:space="preserve">人口加成</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">high_quality_population_bonus</t>
+          <t xml:space="preserve">高素质人口加成</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">happiness_index_bonus</t>
+          <t xml:space="preserve">幸福度加成</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">per_capita_income_bonus</t>
+          <t xml:space="preserve">人均收益加成</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_reduction_bonus</t>
+          <t xml:space="preserve">减碳加成</t>
         </is>
       </c>
     </row>
@@ -1292,22 +4290,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">仓库名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">仓库种类</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacity</t>
+          <t xml:space="preserve">容量</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
     </row>
@@ -1346,17 +4344,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">零件名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">materials</t>
+          <t xml:space="preserve">原料配比</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tech</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
     </row>
@@ -1390,27 +4388,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">比赛名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">map_background_url</t>
+          <t xml:space="preserve">地图背景图地址</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">map_background_width</t>
+          <t xml:space="preserve">背景图宽</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">map_background_height</t>
+          <t xml:space="preserve">背景图高</t>
         </is>
       </c>
     </row>
@@ -1439,17 +4437,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">parts</t>
+          <t xml:space="preserve">零件配比</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tech</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
     </row>
@@ -1483,37 +4481,37 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">载具名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">path_types</t>
+          <t xml:space="preserve">可通行路径类型</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel_consumption_per_km</t>
+          <t xml:space="preserve">每公里油耗</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_cargo</t>
+          <t xml:space="preserve">载货量</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_emission</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
     </row>
@@ -1567,22 +4565,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">product</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantity</t>
+          <t xml:space="preserve">需求量</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">备注</t>
         </is>
       </c>
     </row>
@@ -1621,32 +4619,32 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">company</t>
+          <t xml:space="preserve">公司名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_key</t>
+          <t xml:space="preserve">字段键</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">display_name</t>
+          <t xml:space="preserve">卡片标题</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone</t>
+          <t xml:space="preserve">分区标记</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">card_id</t>
+          <t xml:space="preserve">卡片ID</t>
         </is>
       </c>
     </row>
@@ -1685,47 +4683,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">类型标识</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">合同名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">脚本路径</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">party_roles</t>
+          <t xml:space="preserve">参与方</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">input_schema</t>
+          <t xml:space="preserve">输入项定义</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">effects</t>
+          <t xml:space="preserve">效果定义</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">conditions</t>
+          <t xml:space="preserve">前置检查</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">enabled</t>
+          <t xml:space="preserve">是否启用</t>
         </is>
       </c>
     </row>
@@ -1769,27 +4767,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contract_type</t>
+          <t xml:space="preserve">合同类型标识</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">合同名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">parties</t>
+          <t xml:space="preserve">参与方</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inputs</t>
+          <t xml:space="preserve">输入项</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
     </row>
@@ -1833,27 +4831,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">标题</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">content</t>
+          <t xml:space="preserve">正文</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_all</t>
+          <t xml:space="preserve">是否发给全体</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_users</t>
+          <t xml:space="preserve">指定收件人</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sender</t>
+          <t xml:space="preserve">发布者</t>
         </is>
       </c>
     </row>
@@ -1887,47 +4885,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">username</t>
+          <t xml:space="preserve">用户名</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">角色</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">display_name</t>
+          <t xml:space="preserve">显示名</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">company_scopes</t>
+          <t xml:space="preserve">公司管理范围</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">view_company_scopes</t>
+          <t xml:space="preserve">查看范围</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contract_view_company_scopes</t>
+          <t xml:space="preserve">合同查看范围</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stock_company_scopes</t>
+          <t xml:space="preserve">股票范围</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">permissions</t>
+          <t xml:space="preserve">权限键</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">is_active</t>
+          <t xml:space="preserve">是否启用</t>
         </is>
       </c>
     </row>
@@ -1981,12 +4979,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">year</t>
+          <t xml:space="preserve">年份</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
     </row>
@@ -2015,22 +5013,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">code</t>
+          <t xml:space="preserve">编码</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">产业名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon</t>
+          <t xml:space="preserve">图标</t>
         </is>
       </c>
     </row>
@@ -2064,67 +5062,67 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry_type</t>
+          <t xml:space="preserve">所属产业</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">字段名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_key</t>
+          <t xml:space="preserve">字段键</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_type</t>
+          <t xml:space="preserve">字段类型</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">default_value</t>
+          <t xml:space="preserve">默认值</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">is_calculated</t>
+          <t xml:space="preserve">是否计算字段</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">graph</t>
+          <t xml:space="preserve">计算图</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_enabled</t>
+          <t xml:space="preserve">启用财年定时器</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_trigger</t>
+          <t xml:space="preserve">定时器时机</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_value</t>
+          <t xml:space="preserve">定时器写入值</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sort_order</t>
+          <t xml:space="preserve">排序</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t xml:space="preserve">visible</t>
+          <t xml:space="preserve">是否展示</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t xml:space="preserve">config</t>
+          <t xml:space="preserve">类型配置</t>
         </is>
       </c>
     </row>
@@ -2178,12 +5176,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
     </row>
@@ -2212,47 +5210,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">公司名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry_type</t>
+          <t xml:space="preserve">所属产业</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">所属区域</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">location</t>
+          <t xml:space="preserve">所在地</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">cash</t>
+          <t xml:space="preserve">现金</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank_deposit</t>
+          <t xml:space="preserve">银行存款</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">quota</t>
+          <t xml:space="preserve">许可配额</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inventory</t>
+          <t xml:space="preserve">库存台账</t>
         </is>
       </c>
     </row>
@@ -2301,17 +5299,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">company</t>
+          <t xml:space="preserve">公司名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_key</t>
+          <t xml:space="preserve">字段键</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">值</t>
         </is>
       </c>
     </row>
@@ -2345,17 +5343,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">color</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
     </row>

--- a/backend/examples/excel/比赛建包模板.xlsx
+++ b/backend/examples/excel/比赛建包模板.xlsx
@@ -8,27 +8,21 @@
     <sheet name="产业类型" sheetId="4" r:id="rId4"/>
     <sheet name="产业字段" sheetId="5" r:id="rId5"/>
     <sheet name="区域" sheetId="6" r:id="rId6"/>
-    <sheet name="公司" sheetId="7" r:id="rId7"/>
-    <sheet name="公司字段值" sheetId="8" r:id="rId8"/>
-    <sheet name="地图节点类型" sheetId="9" r:id="rId9"/>
-    <sheet name="路径类型" sheetId="10" r:id="rId10"/>
-    <sheet name="地图节点" sheetId="11" r:id="rId11"/>
-    <sheet name="地图连线" sheetId="12" r:id="rId12"/>
-    <sheet name="燃料" sheetId="13" r:id="rId13"/>
-    <sheet name="原料" sheetId="14" r:id="rId14"/>
-    <sheet name="科技" sheetId="15" r:id="rId15"/>
-    <sheet name="生产线" sheetId="16" r:id="rId16"/>
-    <sheet name="基建" sheetId="17" r:id="rId17"/>
-    <sheet name="仓库" sheetId="18" r:id="rId18"/>
-    <sheet name="零件" sheetId="19" r:id="rId19"/>
-    <sheet name="产品" sheetId="20" r:id="rId20"/>
-    <sheet name="载具" sheetId="21" r:id="rId21"/>
-    <sheet name="消费者需求" sheetId="22" r:id="rId22"/>
-    <sheet name="区域总览卡片" sheetId="23" r:id="rId23"/>
-    <sheet name="合同类型" sheetId="24" r:id="rId24"/>
-    <sheet name="合同实例" sheetId="25" r:id="rId25"/>
-    <sheet name="消息" sheetId="26" r:id="rId26"/>
-    <sheet name="账号" sheetId="27" r:id="rId27"/>
+    <sheet name="地图节点类型" sheetId="7" r:id="rId7"/>
+    <sheet name="路径类型" sheetId="8" r:id="rId8"/>
+    <sheet name="地图节点" sheetId="9" r:id="rId9"/>
+    <sheet name="地图连线" sheetId="10" r:id="rId10"/>
+    <sheet name="燃料" sheetId="11" r:id="rId11"/>
+    <sheet name="原料" sheetId="12" r:id="rId12"/>
+    <sheet name="科技" sheetId="13" r:id="rId13"/>
+    <sheet name="生产线" sheetId="14" r:id="rId14"/>
+    <sheet name="基建" sheetId="15" r:id="rId15"/>
+    <sheet name="仓库" sheetId="16" r:id="rId16"/>
+    <sheet name="零件" sheetId="17" r:id="rId17"/>
+    <sheet name="产品" sheetId="18" r:id="rId18"/>
+    <sheet name="载具" sheetId="19" r:id="rId19"/>
+    <sheet name="消费者需求" sheetId="20" r:id="rId20"/>
+    <sheet name="合同类型" sheetId="21" r:id="rId21"/>
   </sheets>
 </workbook>
 </file>
@@ -67,7 +61,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛建包表格规范 · 使用说明</t>
+          <t xml:space="preserve">比赛建包表格 · 使用说明（本表只建「比赛框架」）</t>
         </is>
       </c>
     </row>
@@ -89,7 +83,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. 第一行是中文表头，**不要改**；需要对照代码时看最后一栏「参数名」。列顺序随意。</t>
+          <t xml:space="preserve">2. 第一行是中文表头，不要改；需要对照代码时看「表头 ↔ 参数名对照」那一节。列顺序随意。</t>
         </is>
       </c>
     </row>
@@ -117,469 +111,313 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6. 股票系统不在本规范内（没有股票 / 资金账户 / 股票参数三类表）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7. 英文参数名同样可用（老文件兼容）；中文表头与参数名指向同一列，不要同时写两列。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t xml:space="preserve">6. 英文参数名同样可用（老文件兼容）；中文表头与参数名指向同一列，不要同时写两列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只建框架，不建运行数据</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">表清单</t>
+          <t xml:space="preserve">本表格覆盖：比赛、财年、行业口径（产业类型 / 产业字段）、区域、地图与路径、物资与产能（燃料 / 原料 / 科技 / 生产线 / 基建 / 仓库 / 零件 / 产品 / 载具）、消费者需求、合同类型。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">表名</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">分组</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">列（* = 必填）</t>
+          <t xml:space="preserve">以下内容绑定具体公司与人，请在界面维护（或用代码建包脚本），不要放进表格：</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">competition</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">比赛本身：名称、状态、地图背景图（整表一行）</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">比赛名称*、状态、地图背景图地址、背景图宽、背景图高</t>
+          <t xml:space="preserve">  · 公司、公司字段初始值 → 公司管理</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">财年</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">competition</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">财年：新建 / 由非 ACTIVE 改为 ACTIVE 会触发 FY_START 定时器</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">年份*、状态</t>
+          <t xml:space="preserve">  · 账号与权限 → 账号管理</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">industry</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全局资源：行业口径（按 code 跨比赛复用，不要给不同行业用同一个 code）</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">编码*、产业名称*、说明、图标</t>
+          <t xml:space="preserve">  · 区域总览卡片 → 区域总览</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">industry</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全局资源：产业下的字段（合同、图表、股票都按 field_key 绑定）</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">所属产业*、字段名称*、字段键*、字段类型、默认值、是否计算字段、计算图、启用财年定时器、定时器时机、定时器写入值、排序、是否展示、类型配置</t>
+          <t xml:space="preserve">  · 比赛内的预置合同（合同实例） → 合同管理</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">company</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">比赛内区域（区域总览、总览卡片按它聚合）</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">区域名称*、说明</t>
+          <t xml:space="preserve">  · 比赛内消息 → 消息中心</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">company</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参赛公司；**额外列会被当作该公司的产业字段初始值**（列名 = field_key）</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公司名称*、所属产业*、所属区域、状态、（额外列：列名写字段键或字段显示名，填公司的产业字段初始值）</t>
+          <t xml:space="preserve">  · 股票 / 资金账户 / 股票参数 → 不启用（按要求不动股票系统）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司字段值</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">company</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">单独维护公司字段值（与公司表二选一或并用，后写覆盖先写）</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公司名称*、字段键*、值</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">地图节点类型</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">geo</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">地图节点分类（矿区 / 港口 / 城市 …）</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">类型名称*、说明、颜色</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">工作簿里若出现这些表名，程序会提示「该去哪里维护」，不会静默忽略。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">geo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">道路类型（公路 / 铁路 / 航运）；载具按它判断可通行</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">类型名称*、说明、颜色</t>
+          <t xml:space="preserve">表清单</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点</t>
+          <t xml:space="preserve">表名</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">geo</t>
+          <t xml:space="preserve">分组</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点（region 是文本列，不是外键）</t>
+          <t xml:space="preserve">用途</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点名称*、节点类型*、所属区域、X坐标、Y坐标</t>
+          <t xml:space="preserve">列（* = 必填）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图连线</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">geo</t>
+          <t xml:space="preserve">competition</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点之间的连线；同一对「起点+终点」只能有一条（反向算另一条）</t>
+          <t xml:space="preserve">比赛本身：名称、状态、地图背景图（整表一行）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">起点节点*、终点节点*、距离(公里)*、路径类型*</t>
+          <t xml:space="preserve">比赛名称*、状态、地图背景图地址、背景图宽、背景图高</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">财年</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">competition</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料（载具必须绑定燃料，外键 PROTECT）</t>
+          <t xml:space="preserve">财年：新建 / 由非 ACTIVE 改为 ACTIVE 会触发 FY_START 定时器</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料名称*、每升单价</t>
+          <t xml:space="preserve">年份*、状态</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">industry</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料（地点价按地图节点名写；运输与运费计算都依赖它）</t>
+          <t xml:space="preserve">全局资源：行业口径（按 code 跨比赛复用，不要给不同行业用同一个 code）</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料名称*、产地、碳排系数、类型、地点价</t>
+          <t xml:space="preserve">编码*、产业名称*、说明、图标</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">industry</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技节点（零件 / 产品按它设前置）</t>
+          <t xml:space="preserve">全局资源：产业下的字段（合同、图表、股票都按 field_key 绑定）</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技名称*、层级、研发费用、说明、前置科技</t>
+          <t xml:space="preserve">所属产业*、字段名称*、字段键*、字段类型、默认值、是否计算字段、计算图、启用财年定时器、定时器时机、定时器写入值、排序、是否展示、类型配置</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线</t>
+          <t xml:space="preserve">区域</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">geo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线（产能与用工人数）</t>
+          <t xml:space="preserve">比赛内区域（区域总览、消费者需求按它聚合）</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线名称*、单价、用工人数、年产能</t>
+          <t xml:space="preserve">区域名称*、说明</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建</t>
+          <t xml:space="preserve">地图节点类型</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">geo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建及其 6 项加成（合同可按清单聚合这些属性）</t>
+          <t xml:space="preserve">地图节点分类（矿区 / 港口 / 城市 …）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建名称*、占地面积、单价、启用费用、就业率加成、人口加成、高素质人口加成、幸福度加成、人均收益加成、减碳加成</t>
+          <t xml:space="preserve">类型名称*、说明、颜色</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">geo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库（MATERIAL / PART / PRODUCT / FUEL 四种建议都覆盖）</t>
+          <t xml:space="preserve">道路类型（公路 / 铁路 / 航运）；载具按它判断可通行</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库名称*、仓库种类*、容量、单价</t>
+          <t xml:space="preserve">类型名称*、说明、颜色</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件</t>
+          <t xml:space="preserve">地图节点</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">geo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件：原料配比 + 科技前置（配比只能引用原料）</t>
+          <t xml:space="preserve">地图节点（region 是文本列，不是外键）</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件名称*、原料配比、所需科技</t>
+          <t xml:space="preserve">节点名称*、节点类型*、所属区域、X坐标、Y坐标</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品</t>
+          <t xml:space="preserve">地图连线</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">geo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品：零件配比 + 科技前置（配比只能引用零件）</t>
+          <t xml:space="preserve">节点之间的连线；同一对「起点+终点」只能有一条（反向算另一条）</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品名称*、零件配比、所需科技</t>
+          <t xml:space="preserve">起点节点*、终点节点*、距离(公里)*、路径类型*</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -589,272 +427,267 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具：绑定燃料 + 可通行路径类型（缺路径类型会导致运输校验失败）</t>
+          <t xml:space="preserve">燃料（载具必须绑定燃料，外键 PROTECT）</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具名称*、燃料*、可通行路径类型、每公里油耗、载货量、单价、碳排系数</t>
+          <t xml:space="preserve">燃料名称*、每升单价</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费者需求</t>
+          <t xml:space="preserve">原料</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">tech</t>
+          <t xml:space="preserve">supply</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域消费者需求（导入按「区域+产品+数量」去重，改数量 = 新增一条）</t>
+          <t xml:space="preserve">原料（地点价按地图节点名写；运输与运费计算都依赖它）</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称*、产品名称*、需求量*、备注</t>
+          <t xml:space="preserve">原料名称*、产地、碳排系数、类型、地点价</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域总览卡片</t>
+          <t xml:space="preserve">科技</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">market</t>
+          <t xml:space="preserve">supply</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域总览卡片（industryFieldId 由建包库自动回填，见文档两遍导入）</t>
+          <t xml:space="preserve">科技节点（零件 / 产品按它设前置）</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称*、公司名称*、字段键*、卡片标题、分区标记、卡片ID</t>
+          <t xml:space="preserve">科技名称*、层级、研发费用、说明、前置科技</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">合同类型</t>
+          <t xml:space="preserve">生产线</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">market</t>
+          <t xml:space="preserve">supply</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局资源：合同模板。四份 JSON 可写 JSON，也可用 `script` 列指向合同类型代码化脚本</t>
+          <t xml:space="preserve">生产线（产能与用工人数）</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型标识*、合同名称*、说明、脚本路径、参与方、输入项定义、效果定义、前置检查、是否启用</t>
+          <t xml:space="preserve">生产线名称*、单价、用工人数、年产能</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">合同实例</t>
+          <t xml:space="preserve">基建</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">market</t>
+          <t xml:space="preserve">supply</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛内的预置合同（保持 DRAFT 不落账）。名称缺省取合同类型名，故每种类型只预置一份</t>
+          <t xml:space="preserve">基建及其 6 项加成（合同可按清单聚合这些属性）</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">合同类型标识*、合同名称、参与方、输入项、状态</t>
+          <t xml:space="preserve">基建名称*、占地面积、单价、启用费用、就业率加成、人口加成、高素质人口加成、幸福度加成、人均收益加成、减碳加成</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">消息</t>
+          <t xml:space="preserve">仓库</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">market</t>
+          <t xml:space="preserve">supply</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛内消息（导入不做判重：重复导入会多建，注意去重）</t>
+          <t xml:space="preserve">仓库（MATERIAL / PART / PRODUCT / FUEL 四种建议都覆盖）</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">标题*、正文、是否发给全体、指定收件人、发布者</t>
+          <t xml:space="preserve">仓库名称*、仓库种类*、容量、单价</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">账号</t>
+          <t xml:space="preserve">零件</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">access</t>
+          <t xml:space="preserve">supply</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">参赛账号与四套公司范围（范围为空 = 登录后什么都看不到）</t>
+          <t xml:space="preserve">零件：原料配比 + 科技前置（配比只能引用原料）</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">用户名*、角色、显示名、公司管理范围、查看范围、合同查看范围、股票范围、权限键、是否启用</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
+          <t xml:space="preserve">零件名称*、原料配比、所需科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产品</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">supply</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产品：零件配比 + 科技前置（配比只能引用零件）</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产品名称*、零件配比、所需科技</t>
+        </is>
+      </c>
+    </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">表头 ↔ 参数名对照</t>
+          <t xml:space="preserve">载具</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">supply</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载具：绑定燃料 + 可通行路径类型（缺路径类型会导致运输校验失败）</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载具名称*、燃料*、可通行路径类型、每公里油耗、载货量、单价、碳排系数</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">表名</t>
+          <t xml:space="preserve">消费者需求</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">中文表头</t>
+          <t xml:space="preserve">tech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">参数名</t>
+          <t xml:space="preserve">区域消费者需求（导入按「区域+产品+数量」去重，改数量 = 新增一条）</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">必填</t>
+          <t xml:space="preserve">区域名称*、产品名称*、需求量*、备注</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛名称</t>
+          <t xml:space="preserve">market</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">全局资源：合同模板。四份 JSON 可写 JSON，也可用 `script` 列指向合同类型代码化脚本</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">比赛</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">状态</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">status</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">类型标识*、合同名称*、说明、脚本路径、参与方、输入项定义、效果定义、前置检查、是否启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">地图背景图地址</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">map_background_url</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">表头 ↔ 参数名对照</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛</t>
+          <t xml:space="preserve">表名</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">背景图宽</t>
+          <t xml:space="preserve">中文表头</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">map_background_width</t>
+          <t xml:space="preserve">参数名</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">类型</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必填</t>
         </is>
       </c>
     </row>
@@ -866,61 +699,61 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">背景图高</t>
+          <t xml:space="preserve">比赛名称</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">map_background_height</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">财年</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">年份</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">year</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">财年</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">状态</t>
+          <t xml:space="preserve">地图背景图地址</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">map_background_url</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -932,93 +765,88 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">编码</t>
+          <t xml:space="preserve">背景图宽</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">code</t>
+          <t xml:space="preserve">map_background_width</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t xml:space="preserve">数字（可按文本填写以保精度）</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业名称</t>
+          <t xml:space="preserve">背景图高</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">map_background_height</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
+          <t xml:space="preserve">财年</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">年份</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">year</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
+          <t xml:space="preserve">财年</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">图标</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1030,22 +858,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属产业</t>
+          <t xml:space="preserve">编码</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry_type</t>
+          <t xml:space="preserve">code</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1057,12 +885,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段名称</t>
+          <t xml:space="preserve">产业名称</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1084,44 +912,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段键</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_key</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段类型</t>
+          <t xml:space="preserve">图标</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_type</t>
+          <t xml:space="preserve">icon</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1138,17 +961,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认值</t>
+          <t xml:space="preserve">所属产业</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">default_value</t>
+          <t xml:space="preserve">industry_type</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -1160,17 +988,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否计算字段</t>
+          <t xml:space="preserve">字段名称</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">is_calculated</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">是/否</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -1182,17 +1015,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">计算图</t>
+          <t xml:space="preserve">字段键</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">graph</t>
+          <t xml:space="preserve">field_key</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON 文本</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -1204,17 +1042,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">启用财年定时器</t>
+          <t xml:space="preserve">字段类型</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_enabled</t>
+          <t xml:space="preserve">field_type</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">是/否</t>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1064,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">定时器时机</t>
+          <t xml:space="preserve">默认值</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_trigger</t>
+          <t xml:space="preserve">default_value</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1248,17 +1086,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">定时器写入值</t>
+          <t xml:space="preserve">是否计算字段</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_value</t>
+          <t xml:space="preserve">is_calculated</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">是/否</t>
         </is>
       </c>
     </row>
@@ -1270,17 +1108,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">排序</t>
+          <t xml:space="preserve">计算图</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">sort_order</t>
+          <t xml:space="preserve">graph</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">JSON 文本</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1130,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否展示</t>
+          <t xml:space="preserve">启用财年定时器</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">visible</t>
+          <t xml:space="preserve">timer_enabled</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1314,12 +1152,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型配置</t>
+          <t xml:space="preserve">定时器时机</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">config</t>
+          <t xml:space="preserve">timer_trigger</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1331,142 +1169,132 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称</t>
+          <t xml:space="preserve">定时器写入值</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">timer_value</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">排序</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">sort_order</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司名称</t>
+          <t xml:space="preserve">是否展示</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">visible</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">是/否</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属产业</t>
+          <t xml:space="preserve">类型配置</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry_type</t>
+          <t xml:space="preserve">config</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司</t>
+          <t xml:space="preserve">区域</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属区域</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司</t>
+          <t xml:space="preserve">区域</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">状态</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1478,17 +1306,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司字段值</t>
+          <t xml:space="preserve">地图节点类型</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司名称</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">company</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1505,44 +1333,39 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司字段值</t>
+          <t xml:space="preserve">地图节点类型</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段键</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_key</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司字段值</t>
+          <t xml:space="preserve">地图节点类型</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">值</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">color</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1554,7 +1377,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点类型</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1581,7 +1404,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点类型</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1603,7 +1426,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点类型</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1625,12 +1448,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">地图节点</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型名称</t>
+          <t xml:space="preserve">节点名称</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1652,39 +1475,44 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">地图节点</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">节点类型</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">node_type</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">地图节点</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">颜色</t>
+          <t xml:space="preserve">所属区域</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">color</t>
+          <t xml:space="preserve">region</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1701,22 +1529,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点名称</t>
+          <t xml:space="preserve">X坐标</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">x</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
@@ -1728,88 +1551,98 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点类型</t>
+          <t xml:space="preserve">Y坐标</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">node_type</t>
+          <t xml:space="preserve">y</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点</t>
+          <t xml:space="preserve">地图连线</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属区域</t>
+          <t xml:space="preserve">起点节点</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">from_node</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点</t>
+          <t xml:space="preserve">地图连线</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">X坐标</t>
+          <t xml:space="preserve">终点节点</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">x</t>
+          <t xml:space="preserve">to_node</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点</t>
+          <t xml:space="preserve">地图连线</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y坐标</t>
+          <t xml:space="preserve">距离(公里)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">y</t>
+          <t xml:space="preserve">distance</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
           <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1654,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">起点节点</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_node</t>
+          <t xml:space="preserve">path_type</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -1843,17 +1676,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图连线</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">终点节点</t>
+          <t xml:space="preserve">燃料名称</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_node</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -1870,44 +1703,39 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图连线</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">距离(公里)</t>
+          <t xml:space="preserve">每升单价</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">distance</t>
+          <t xml:space="preserve">price_per_liter</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t xml:space="preserve">数字（可按文本填写以保精度）</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图连线</t>
+          <t xml:space="preserve">原料</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">原料名称</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">path_type</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -1924,44 +1752,39 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">原料</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料名称</t>
+          <t xml:space="preserve">产地</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">origin</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">原料</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">每升单价</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">price_per_liter</t>
+          <t xml:space="preserve">carbon_emission_coefficient</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -1978,22 +1801,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料名称</t>
+          <t xml:space="preserve">类型</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -2005,83 +1823,88 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">产地</t>
+          <t xml:space="preserve">地点价</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">origin</t>
+          <t xml:space="preserve">node_prices</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料</t>
+          <t xml:space="preserve">科技</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">碳排系数</t>
+          <t xml:space="preserve">科技名称</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_emission_coefficient</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料</t>
+          <t xml:space="preserve">科技</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型</t>
+          <t xml:space="preserve">层级</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">tier</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料</t>
+          <t xml:space="preserve">科技</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">地点价</t>
+          <t xml:space="preserve">研发费用</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">node_prices</t>
+          <t xml:space="preserve">research_cost</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
@@ -2093,22 +1916,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技名称</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -2120,83 +1938,88 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">层级</t>
+          <t xml:space="preserve">前置科技</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">prerequisites</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">列表（分号分隔）</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技</t>
+          <t xml:space="preserve">生产线</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">研发费用</t>
+          <t xml:space="preserve">生产线名称</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">research_cost</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技</t>
+          <t xml:space="preserve">生产线</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技</t>
+          <t xml:space="preserve">生产线</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">前置科技</t>
+          <t xml:space="preserve">用工人数</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">prerequisites</t>
+          <t xml:space="preserve">labor_count</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
@@ -2208,61 +2031,61 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线名称</t>
+          <t xml:space="preserve">年产能</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">max_per_year</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线</t>
+          <t xml:space="preserve">基建</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">基建名称</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线</t>
+          <t xml:space="preserve">基建</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">用工人数</t>
+          <t xml:space="preserve">占地面积</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">labor_count</t>
+          <t xml:space="preserve">footprint</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2274,17 +2097,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线</t>
+          <t xml:space="preserve">基建</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">年产能</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_per_year</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2301,22 +2124,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建名称</t>
+          <t xml:space="preserve">启用费用</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">activation_price</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2146,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">占地面积</t>
+          <t xml:space="preserve">就业率加成</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">footprint</t>
+          <t xml:space="preserve">employment_rate_bonus</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2350,12 +2168,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">人口加成</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">population_bonus</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2372,12 +2190,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">启用费用</t>
+          <t xml:space="preserve">高素质人口加成</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">activation_price</t>
+          <t xml:space="preserve">high_quality_population_bonus</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2394,12 +2212,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">就业率加成</t>
+          <t xml:space="preserve">幸福度加成</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">employment_rate_bonus</t>
+          <t xml:space="preserve">happiness_index_bonus</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2416,12 +2234,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">人口加成</t>
+          <t xml:space="preserve">人均收益加成</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">population_bonus</t>
+          <t xml:space="preserve">per_capita_income_bonus</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2438,12 +2256,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">高素质人口加成</t>
+          <t xml:space="preserve">减碳加成</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">high_quality_population_bonus</t>
+          <t xml:space="preserve">carbon_reduction_bonus</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2455,61 +2273,71 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建</t>
+          <t xml:space="preserve">仓库</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">幸福度加成</t>
+          <t xml:space="preserve">仓库名称</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">happiness_index_bonus</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建</t>
+          <t xml:space="preserve">仓库</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">人均收益加成</t>
+          <t xml:space="preserve">仓库种类</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">per_capita_income_bonus</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建</t>
+          <t xml:space="preserve">仓库</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">减碳加成</t>
+          <t xml:space="preserve">容量</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_reduction_bonus</t>
+          <t xml:space="preserve">capacity</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2526,39 +2354,34 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库名称</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库</t>
+          <t xml:space="preserve">零件</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库种类</t>
+          <t xml:space="preserve">零件名称</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2575,56 +2398,56 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库</t>
+          <t xml:space="preserve">零件</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">容量</t>
+          <t xml:space="preserve">原料配比</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacity</t>
+          <t xml:space="preserve">materials</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库</t>
+          <t xml:space="preserve">零件</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">tech</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">列表（分号分隔）</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件</t>
+          <t xml:space="preserve">产品</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件名称</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2646,17 +2469,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件</t>
+          <t xml:space="preserve">产品</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料配比</t>
+          <t xml:space="preserve">零件配比</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">materials</t>
+          <t xml:space="preserve">parts</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2668,7 +2491,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件</t>
+          <t xml:space="preserve">产品</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2690,12 +2513,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品</t>
+          <t xml:space="preserve">载具</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品名称</t>
+          <t xml:space="preserve">载具名称</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2717,39 +2540,44 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品</t>
+          <t xml:space="preserve">载具</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件配比</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">parts</t>
+          <t xml:space="preserve">fuel</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品</t>
+          <t xml:space="preserve">载具</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">所需科技</t>
+          <t xml:space="preserve">可通行路径类型</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">tech</t>
+          <t xml:space="preserve">path_types</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -2766,22 +2594,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具名称</t>
+          <t xml:space="preserve">每公里油耗</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">fuel_consumption_per_km</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
@@ -2793,22 +2616,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">载货量</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel</t>
+          <t xml:space="preserve">max_cargo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2638,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">可通行路径类型</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">path_types</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
@@ -2842,12 +2660,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">每公里油耗</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel_consumption_per_km</t>
+          <t xml:space="preserve">carbon_emission</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2859,66 +2677,81 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具</t>
+          <t xml:space="preserve">消费者需求</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">载货量</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_cargo</t>
+          <t xml:space="preserve">region</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具</t>
+          <t xml:space="preserve">消费者需求</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">product</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具</t>
+          <t xml:space="preserve">消费者需求</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">碳排系数</t>
+          <t xml:space="preserve">需求量</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_emission</t>
+          <t xml:space="preserve">quantity</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
           <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -2930,39 +2763,34 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称</t>
+          <t xml:space="preserve">备注</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费者需求</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品名称</t>
+          <t xml:space="preserve">类型标识</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">product</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -2979,22 +2807,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费者需求</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">需求量</t>
+          <t xml:space="preserve">合同名称</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantity</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -3006,17 +2834,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费者需求</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">备注</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3028,786 +2856,130 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域总览卡片</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称</t>
+          <t xml:space="preserve">脚本路径</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域总览卡片</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司名称</t>
+          <t xml:space="preserve">参与方</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">company</t>
+          <t xml:space="preserve">party_roles</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">JSON 文本</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域总览卡片</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段键</t>
+          <t xml:space="preserve">输入项定义</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_key</t>
+          <t xml:space="preserve">input_schema</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">JSON 文本</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域总览卡片</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">卡片标题</t>
+          <t xml:space="preserve">效果定义</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">display_name</t>
+          <t xml:space="preserve">effects</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">JSON 文本</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域总览卡片</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">分区标记</t>
+          <t xml:space="preserve">前置检查</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone</t>
+          <t xml:space="preserve">conditions</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">JSON 文本</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域总览卡片</t>
+          <t xml:space="preserve">合同类型</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">卡片ID</t>
+          <t xml:space="preserve">是否启用</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">card_id</t>
+          <t xml:space="preserve">enabled</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">类型标识</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同名称</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">description</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">脚本路径</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">script</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参与方</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">party_roles</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入项定义</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">input_schema</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">效果定义</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">effects</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前置检查</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">conditions</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否启用</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">enabled</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是/否</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同实例</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型标识</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contract_type</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同实例</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同名称</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同实例</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参与方</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parties</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同实例</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入项</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inputs</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">键值（key=value，分号分隔）</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同实例</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">状态</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">status</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">消息</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">标题</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">title</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">消息</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">正文</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">content</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">消息</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否发给全体</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">to_all</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是/否</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">消息</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">指定收件人</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">to_users</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">消息</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发布者</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sender</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">账号</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用户名</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">username</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">账号</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">角色</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">role</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">账号</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">显示名</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">display_name</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">账号</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公司管理范围</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">company_scopes</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">账号</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">查看范围</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">view_company_scopes</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">账号</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同查看范围</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contract_view_company_scopes</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">账号</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">股票范围</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stock_company_scopes</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">账号</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">权限键</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">permissions</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">账号</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否启用</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">is_active</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
         <is>
           <t xml:space="preserve">是/否</t>
         </is>
@@ -3823,34 +2995,44 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型名称</t>
+          <t xml:space="preserve">起点节点</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">终点节点</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">颜色</t>
+          <t xml:space="preserve">距离(公里)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">白云鄂博矿区</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上游集运站</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t xml:space="preserve">公路</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通用公路运输</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#94a3b8</t>
         </is>
       </c>
     </row>
@@ -3867,54 +3049,24 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点名称</t>
+          <t xml:space="preserve">燃料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点类型</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">所属区域</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X坐标</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y坐标</t>
+          <t xml:space="preserve">每升单价</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">白云鄂博矿区</t>
+          <t xml:space="preserve">柴油</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿区</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">7.6</t>
         </is>
       </c>
     </row>
@@ -3931,44 +3083,54 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">起点节点</t>
+          <t xml:space="preserve">原料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">终点节点</t>
+          <t xml:space="preserve">产地</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">距离(公里)</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">类型</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地点价</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">锂矿石</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">白云鄂博矿区</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游集运站</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">0.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白云鄂博矿区:180; 上游集运站:195</t>
         </is>
       </c>
     </row>
@@ -3985,24 +3147,49 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料名称</t>
+          <t xml:space="preserve">科技名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">每升单价</t>
+          <t xml:space="preserve">层级</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">研发费用</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前置科技</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">柴油</t>
+          <t xml:space="preserve">电池成组技术</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.6</t>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">解锁动力电池包</t>
         </is>
       </c>
     </row>
@@ -4019,54 +3206,44 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料名称</t>
+          <t xml:space="preserve">生产线名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">产地</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">碳排系数</t>
+          <t xml:space="preserve">用工人数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">地点价</t>
+          <t xml:space="preserve">年产能</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">锂矿石</t>
+          <t xml:space="preserve">电芯产线</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">白云鄂博矿区</t>
+          <t xml:space="preserve">2400000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.52</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORMAL</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白云鄂博矿区:180; 上游集运站:195</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
     </row>
@@ -4083,49 +3260,84 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技名称</t>
+          <t xml:space="preserve">基建名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">层级</t>
+          <t xml:space="preserve">占地面积</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">研发费用</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">启用费用</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">前置科技</t>
+          <t xml:space="preserve">就业率加成</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人口加成</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高素质人口加成</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幸福度加成</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人均收益加成</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">减碳加成</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">电池成组技术</t>
+          <t xml:space="preserve">光伏电站</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">160</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80000</t>
+          <t xml:space="preserve">1200000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">解锁动力电池包</t>
+          <t xml:space="preserve">50000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.02</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.12</t>
         </is>
       </c>
     </row>
@@ -4142,44 +3354,44 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线名称</t>
+          <t xml:space="preserve">仓库名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t xml:space="preserve">仓库种类</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">容量</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t xml:space="preserve">单价</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用工人数</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">年产能</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">电芯产线</t>
+          <t xml:space="preserve">原料仓</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400000</t>
+          <t xml:space="preserve">MATERIAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">30000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">400000</t>
         </is>
       </c>
     </row>
@@ -4196,84 +3408,34 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建名称</t>
+          <t xml:space="preserve">零件名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">占地面积</t>
+          <t xml:space="preserve">原料配比</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">启用费用</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">就业率加成</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">人口加成</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高素质人口加成</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">幸福度加成</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">人均收益加成</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">减碳加成</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">光伏电站</t>
+          <t xml:space="preserve">动力电池包</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160</t>
+          <t xml:space="preserve">锂矿石*4; 铝土矿*1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.02</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.12</t>
+          <t xml:space="preserve">电池成组技术</t>
         </is>
       </c>
     </row>
@@ -4290,44 +3452,34 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库名称</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库种类</t>
+          <t xml:space="preserve">零件配比</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">容量</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料仓</t>
+          <t xml:space="preserve">纯电轿车</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATERIAL</t>
+          <t xml:space="preserve">动力电池包*1; 驱动电机*1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400000</t>
+          <t xml:space="preserve">整车平台化</t>
         </is>
       </c>
     </row>
@@ -4344,34 +3496,74 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件名称</t>
+          <t xml:space="preserve">载具名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料配比</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所需科技</t>
+          <t xml:space="preserve">可通行路径类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每公里油耗</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载货量</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单价</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">动力电池包</t>
+          <t xml:space="preserve">重型卡车</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">锂矿石*4; 铝土矿*1</t>
+          <t xml:space="preserve">柴油</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">电池成组技术</t>
+          <t xml:space="preserve">公路</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.35</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9</t>
         </is>
       </c>
     </row>
@@ -4437,34 +3629,44 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">区域名称</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t xml:space="preserve">产品名称</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">零件配比</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所需科技</t>
+          <t xml:space="preserve">需求量</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">备注</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">东部车都</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">纯电轿车</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">动力电池包*1; 驱动电机*1</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">整车平台化</t>
+          <t xml:space="preserve">1200</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">城市通勤主力车型</t>
         </is>
       </c>
     </row>
@@ -4481,483 +3683,69 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具名称</t>
+          <t xml:space="preserve">类型标识</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">合同名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">可通行路径类型</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">每公里油耗</t>
+          <t xml:space="preserve">脚本路径</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">载货量</t>
+          <t xml:space="preserve">参与方</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">输入项定义</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">碳排系数</t>
+          <t xml:space="preserve">效果定义</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前置检查</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否启用</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">重型卡车</t>
+          <t xml:space="preserve">auto-mining</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">柴油</t>
+          <t xml:space="preserve">开采合同</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
+          <t xml:space="preserve">开采企业缴纳权利金并入库原矿</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.35</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">区域名称</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">产品名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">需求量</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">东部车都</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">纯电轿车</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1200</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">城市通勤主力车型</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">区域名称</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公司名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">字段键</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">卡片标题</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">分区标记</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">卡片ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cash</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业现金</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">类型标识</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">脚本路径</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参与方</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入项定义</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">效果定义</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前置检查</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否启用</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto-mining</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开采合同</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开采企业缴纳权利金并入库原矿</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型标识</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参与方</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入项</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">auto-mining</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开采合同</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">miner=西岭锂业|MIN-2026-001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ore_type=锂矿石; quantity=20; royalty_rate=60</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DRAFT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">标题</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">正文</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否发给全体</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">指定收件人</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发布者</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开局公告</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">欢迎参赛，请先核对本公司初始字段。</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用户名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">角色</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">显示名</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公司管理范围</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">查看范围</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同查看范围</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">股票范围</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">权限键</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否启用</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">player_a</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLAYER</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">玩家A</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业;中原创能</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业;中原创能</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">西岭锂业;中原创能</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -5210,79 +3998,34 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司名称</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属产业</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属区域</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">状态</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">所在地</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">现金</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">银行存款</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">许可配额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">库存台账</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">西岭锂业</t>
+          <t xml:space="preserve">矿区</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料开采</t>
+          <t xml:space="preserve">原矿开采地</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTIVE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白云鄂博矿区</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1200000</t>
+          <t xml:space="preserve">#b45309</t>
         </is>
       </c>
     </row>
@@ -5299,34 +4042,34 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司名称</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段键</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">值</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">西岭锂业</t>
+          <t xml:space="preserve">公路</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank_deposit</t>
+          <t xml:space="preserve">通用公路运输</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300000</t>
+          <t xml:space="preserve">#94a3b8</t>
         </is>
       </c>
     </row>
@@ -5343,34 +4086,54 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型名称</t>
+          <t xml:space="preserve">节点名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">节点类型</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">颜色</t>
+          <t xml:space="preserve">所属区域</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X坐标</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y坐标</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">白云鄂博矿区</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">矿区</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">原矿开采地</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#b45309</t>
+          <t xml:space="preserve">上游资源区</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
     </row>

--- a/backend/examples/excel/比赛建包模板.xlsx
+++ b/backend/examples/excel/比赛建包模板.xlsx
@@ -647,12 +647,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局资源：合同模板。四份 JSON 可写 JSON，也可用 `script` 列指向合同类型代码化脚本</t>
+          <t xml:space="preserve">合同类型**只由代码脚本创建**（合同类型代码化建库）：本表只写脚本路径与要引入的类型标识</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型标识*、合同名称*、说明、脚本路径、参与方、输入项定义、效果定义、前置检查、是否启用</t>
+          <t xml:space="preserve">脚本路径*、类型标识、是否启用</t>
         </is>
       </c>
     </row>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型标识</t>
+          <t xml:space="preserve">脚本路径</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -2812,22 +2812,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">合同名称</t>
+          <t xml:space="preserve">类型标识</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -2839,147 +2834,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">是否启用</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">enabled</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">脚本路径</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">script</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参与方</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">party_roles</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入项定义</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">input_schema</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">效果定义</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">effects</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前置检查</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">conditions</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JSON 文本</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同类型</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否启用</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">enabled</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
         <is>
           <t xml:space="preserve">是/否</t>
         </is>
@@ -3683,45 +3546,15 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">脚本路径</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t xml:space="preserve">类型标识</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同名称</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">脚本路径</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参与方</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入项定义</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">效果定义</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前置检查</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">是否启用</t>
         </is>
@@ -3730,25 +3563,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">auto-mining</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开采合同</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开采企业缴纳权利金并入库原矿</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">examples/contracts/auto_chain_contracts.py</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">是</t>
         </is>

--- a/backend/examples/excel/比赛建包模板.xlsx
+++ b/backend/examples/excel/比赛建包模板.xlsx
@@ -5,24 +5,25 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="比赛" sheetId="2" r:id="rId2"/>
     <sheet name="财年" sheetId="3" r:id="rId3"/>
-    <sheet name="产业类型" sheetId="4" r:id="rId4"/>
-    <sheet name="产业字段" sheetId="5" r:id="rId5"/>
-    <sheet name="区域" sheetId="6" r:id="rId6"/>
-    <sheet name="地图节点类型" sheetId="7" r:id="rId7"/>
-    <sheet name="路径类型" sheetId="8" r:id="rId8"/>
-    <sheet name="地图节点" sheetId="9" r:id="rId9"/>
-    <sheet name="地图连线" sheetId="10" r:id="rId10"/>
-    <sheet name="燃料" sheetId="11" r:id="rId11"/>
-    <sheet name="原料" sheetId="12" r:id="rId12"/>
-    <sheet name="科技" sheetId="13" r:id="rId13"/>
-    <sheet name="生产线" sheetId="14" r:id="rId14"/>
-    <sheet name="基建" sheetId="15" r:id="rId15"/>
-    <sheet name="仓库" sheetId="16" r:id="rId16"/>
-    <sheet name="零件" sheetId="17" r:id="rId17"/>
-    <sheet name="产品" sheetId="18" r:id="rId18"/>
-    <sheet name="载具" sheetId="19" r:id="rId19"/>
-    <sheet name="消费者需求" sheetId="20" r:id="rId20"/>
-    <sheet name="合同类型" sheetId="21" r:id="rId21"/>
+    <sheet name="股票参数" sheetId="4" r:id="rId4"/>
+    <sheet name="产业类型" sheetId="5" r:id="rId5"/>
+    <sheet name="产业字段" sheetId="6" r:id="rId6"/>
+    <sheet name="区域" sheetId="7" r:id="rId7"/>
+    <sheet name="地图节点类型" sheetId="8" r:id="rId8"/>
+    <sheet name="路径类型" sheetId="9" r:id="rId9"/>
+    <sheet name="地图节点" sheetId="10" r:id="rId10"/>
+    <sheet name="地图连线" sheetId="11" r:id="rId11"/>
+    <sheet name="燃料" sheetId="12" r:id="rId12"/>
+    <sheet name="原料" sheetId="13" r:id="rId13"/>
+    <sheet name="科技" sheetId="14" r:id="rId14"/>
+    <sheet name="生产线" sheetId="15" r:id="rId15"/>
+    <sheet name="基建" sheetId="16" r:id="rId16"/>
+    <sheet name="仓库" sheetId="17" r:id="rId17"/>
+    <sheet name="零件" sheetId="18" r:id="rId18"/>
+    <sheet name="产品" sheetId="19" r:id="rId19"/>
+    <sheet name="载具" sheetId="20" r:id="rId20"/>
+    <sheet name="消费者需求" sheetId="21" r:id="rId21"/>
+    <sheet name="合同类型" sheetId="22" r:id="rId22"/>
   </sheets>
 </workbook>
 </file>
@@ -126,7 +127,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">本表格覆盖：比赛、财年、行业口径（产业类型 / 产业字段）、区域、地图与路径、物资与产能（燃料 / 原料 / 科技 / 生产线 / 基建 / 仓库 / 零件 / 产品 / 载具）、消费者需求、合同类型。</t>
+          <t xml:space="preserve">本表格覆盖：比赛、财年、股票参数（市场规则）、行业口径（产业类型 / 产业字段）、区域、地图与路径、物资与产能（燃料 / 原料 / 科技 / 生产线 / 基建 / 仓库 / 零件 / 产品 / 载具）、消费者需求、合同类型（由代码脚本产出）。</t>
         </is>
       </c>
     </row>
@@ -175,73 +176,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 股票 / 资金账户 / 股票参数 → 不启用（按要求不动股票系统）</t>
+          <t xml:space="preserve">  · 个股、资金账户 → 股票管理（PE 联动公司/字段、资金账户绑定字段都是主键引用）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t xml:space="preserve">  · 持仓 / 委托 / K 线 → 撮合与「推进轮次」在运行时生成，无法预置</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t xml:space="preserve">工作簿里若出现这些表名，程序会提示「该去哪里维护」，不会静默忽略。</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">表清单</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">表名</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">分组</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">列（* = 必填）</t>
+          <t xml:space="preserve">表清单</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛</t>
+          <t xml:space="preserve">表名</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">competition</t>
+          <t xml:space="preserve">分组</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛本身：名称、状态、地图背景图（整表一行）</t>
+          <t xml:space="preserve">用途</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛名称*、状态、地图背景图地址、背景图宽、背景图高</t>
+          <t xml:space="preserve">列（* = 必填）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">财年</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -251,107 +237,107 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">财年：新建 / 由非 ACTIVE 改为 ACTIVE 会触发 FY_START 定时器</t>
+          <t xml:space="preserve">比赛本身：名称、状态、地图背景图（整表一行）</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">年份*、状态</t>
+          <t xml:space="preserve">比赛名称*、状态、地图背景图地址、背景图宽、背景图高</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
+          <t xml:space="preserve">财年</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry</t>
+          <t xml:space="preserve">competition</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局资源：行业口径（按 code 跨比赛复用，不要给不同行业用同一个 code）</t>
+          <t xml:space="preserve">财年：新建 / 由非 ACTIVE 改为 ACTIVE 会触发 FY_START 定时器</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">编码*、产业名称*、说明、图标</t>
+          <t xml:space="preserve">年份*、状态</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
+          <t xml:space="preserve">股票参数</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry</t>
+          <t xml:space="preserve">competition</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">全局资源：产业下的字段（合同、图表、股票都按 field_key 绑定）</t>
+          <t xml:space="preserve">股票市场的**规则**（单轮限幅 / 最大波动 / 做市商 / 随机事件…）：键值两列，每行一个参数；留空表示沿用系统默认。个股与资金账户绑定公司/人/主键，不在表格内（去「股票管理」维护）</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属产业*、字段名称*、字段键*、字段类型、默认值、是否计算字段、计算图、启用财年定时器、定时器时机、定时器写入值、排序、是否展示、类型配置</t>
+          <t xml:space="preserve">参数*、值*</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">geo</t>
+          <t xml:space="preserve">industry</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛内区域（区域总览、消费者需求按它聚合）</t>
+          <t xml:space="preserve">全局资源：行业口径（按 code 跨比赛复用，不要给不同行业用同一个 code）</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称*、说明</t>
+          <t xml:space="preserve">编码*、产业名称*、说明、图标</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点类型</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">geo</t>
+          <t xml:space="preserve">industry</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点分类（矿区 / 港口 / 城市 …）</t>
+          <t xml:space="preserve">全局资源：产业下的字段（合同、图表、股票都按 field_key 绑定）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型名称*、说明、颜色</t>
+          <t xml:space="preserve">所属产业*、字段名称*、字段键*、字段类型、默认值、是否计算字段、计算图、启用财年定时器、定时器时机、定时器写入值、排序、是否展示、类型配置</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">区域</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -361,19 +347,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">道路类型（公路 / 铁路 / 航运）；载具按它判断可通行</t>
+          <t xml:space="preserve">比赛内区域（区域总览、消费者需求按它聚合）</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型名称*、说明、颜色</t>
+          <t xml:space="preserve">区域名称*、说明</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点</t>
+          <t xml:space="preserve">地图节点类型</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -383,19 +369,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点（region 是文本列，不是外键）</t>
+          <t xml:space="preserve">地图节点分类（矿区 / 港口 / 城市 …）</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点名称*、节点类型*、所属区域、X坐标、Y坐标</t>
+          <t xml:space="preserve">类型名称*、说明、颜色</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图连线</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -405,63 +391,63 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点之间的连线；同一对「起点+终点」只能有一条（反向算另一条）</t>
+          <t xml:space="preserve">道路类型（公路 / 铁路 / 航运）；载具按它判断可通行</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">起点节点*、终点节点*、距离(公里)*、路径类型*</t>
+          <t xml:space="preserve">类型名称*、说明、颜色</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">地图节点</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">geo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料（载具必须绑定燃料，外键 PROTECT）</t>
+          <t xml:space="preserve">地图节点（region 是文本列，不是外键）</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料名称*、每升单价</t>
+          <t xml:space="preserve">节点名称*、节点类型*、所属区域、X坐标、Y坐标</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料</t>
+          <t xml:space="preserve">地图连线</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">supply</t>
+          <t xml:space="preserve">geo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料（地点价按地图节点名写；运输与运费计算都依赖它）</t>
+          <t xml:space="preserve">节点之间的连线；同一对「起点+终点」只能有一条（反向算另一条）</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料名称*、产地、碳排系数、类型、地点价</t>
+          <t xml:space="preserve">起点节点*、终点节点*、距离(公里)*、路径类型*</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -471,19 +457,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技节点（零件 / 产品按它设前置）</t>
+          <t xml:space="preserve">燃料（载具必须绑定燃料，外键 PROTECT）</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技名称*、层级、研发费用、说明、前置科技</t>
+          <t xml:space="preserve">燃料名称*、每升单价</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线</t>
+          <t xml:space="preserve">原料</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -493,19 +479,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线（产能与用工人数）</t>
+          <t xml:space="preserve">原料（地点价按地图节点名写；运输与运费计算都依赖它）</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线名称*、单价、用工人数、年产能</t>
+          <t xml:space="preserve">原料名称*、产地、碳排系数、类型、地点价</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建</t>
+          <t xml:space="preserve">科技</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -515,19 +501,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建及其 6 项加成（合同可按清单聚合这些属性）</t>
+          <t xml:space="preserve">科技节点（零件 / 产品按它设前置）</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建名称*、占地面积、单价、启用费用、就业率加成、人口加成、高素质人口加成、幸福度加成、人均收益加成、减碳加成</t>
+          <t xml:space="preserve">科技名称*、层级、研发费用、说明、前置科技</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库</t>
+          <t xml:space="preserve">生产线</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -537,19 +523,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库（MATERIAL / PART / PRODUCT / FUEL 四种建议都覆盖）</t>
+          <t xml:space="preserve">生产线（产能与用工人数）</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库名称*、仓库种类*、容量、单价</t>
+          <t xml:space="preserve">生产线名称*、单价、用工人数、年产能</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件</t>
+          <t xml:space="preserve">基建</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -559,19 +545,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件：原料配比 + 科技前置（配比只能引用原料）</t>
+          <t xml:space="preserve">基建及其 6 项加成（合同可按清单聚合这些属性）</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件名称*、原料配比、所需科技</t>
+          <t xml:space="preserve">基建名称*、占地面积、单价、启用费用、就业率加成、人口加成、高素质人口加成、幸福度加成、人均收益加成、减碳加成</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品</t>
+          <t xml:space="preserve">仓库</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -581,19 +567,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品：零件配比 + 科技前置（配比只能引用零件）</t>
+          <t xml:space="preserve">仓库（MATERIAL / PART / PRODUCT / FUEL 四种建议都覆盖）</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品名称*、零件配比、所需科技</t>
+          <t xml:space="preserve">仓库名称*、仓库种类*、容量、单价</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具</t>
+          <t xml:space="preserve">零件</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -603,140 +589,135 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具：绑定燃料 + 可通行路径类型（缺路径类型会导致运输校验失败）</t>
+          <t xml:space="preserve">零件：原料配比 + 科技前置（配比只能引用原料）</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具名称*、燃料*、可通行路径类型、每公里油耗、载货量、单价、碳排系数</t>
+          <t xml:space="preserve">零件名称*、原料配比、所需科技</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费者需求</t>
+          <t xml:space="preserve">产品</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">tech</t>
+          <t xml:space="preserve">supply</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域消费者需求（导入按「区域+产品+数量」去重，改数量 = 新增一条）</t>
+          <t xml:space="preserve">产品：零件配比 + 科技前置（配比只能引用零件）</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称*、产品名称*、需求量*、备注</t>
+          <t xml:space="preserve">产品名称*、零件配比、所需科技</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">合同类型</t>
+          <t xml:space="preserve">载具</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">market</t>
+          <t xml:space="preserve">supply</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">合同类型**只由代码脚本创建**（合同类型代码化建库）：本表只写脚本路径与要引入的类型标识</t>
+          <t xml:space="preserve">载具：绑定燃料 + 可通行路径类型（缺路径类型会导致运输校验失败）</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">脚本路径*、类型标识、是否启用</t>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
+          <t xml:space="preserve">载具名称*、燃料*、可通行路径类型、每公里油耗、载货量、单价、碳排系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消费者需求</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tech</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域消费者需求（导入按「区域+产品+数量」去重，改数量 = 新增一条）</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">区域名称*、产品名称*、需求量*、备注</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">表头 ↔ 参数名对照</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">表名</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中文表头</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参数名</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">类型</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">必填</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">market</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型**只由代码脚本创建**（合同类型代码化建库）：本表只写脚本路径与要引入的类型标识</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">脚本路径*、类型标识、是否启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">比赛名称</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">表头 ↔ 参数名对照</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">比赛</t>
+          <t xml:space="preserve">表名</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">状态</t>
+          <t xml:space="preserve">中文表头</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">参数名</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">类型</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">必填</t>
         </is>
       </c>
     </row>
@@ -748,17 +729,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图背景图地址</t>
+          <t xml:space="preserve">比赛名称</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">map_background_url</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -770,17 +756,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">背景图宽</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">map_background_width</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
     </row>
@@ -792,83 +778,78 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">背景图高</t>
+          <t xml:space="preserve">地图背景图地址</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">map_background_height</t>
+          <t xml:space="preserve">map_background_url</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">财年</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">年份</t>
+          <t xml:space="preserve">背景图宽</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">year</t>
+          <t xml:space="preserve">map_background_width</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
           <t xml:space="preserve">数字（可按文本填写以保精度）</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">财年</t>
+          <t xml:space="preserve">比赛</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">状态</t>
+          <t xml:space="preserve">背景图高</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">map_background_height</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
+          <t xml:space="preserve">财年</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">编码</t>
+          <t xml:space="preserve">年份</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">code</t>
+          <t xml:space="preserve">year</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -885,93 +866,98 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
+          <t xml:space="preserve">财年</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业名称</t>
+          <t xml:space="preserve">状态</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
+          <t xml:space="preserve">股票参数</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">参数</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">param</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业类型</t>
+          <t xml:space="preserve">股票参数</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">图标</t>
+          <t xml:space="preserve">值</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon</t>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属产业</t>
+          <t xml:space="preserve">编码</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">industry_type</t>
+          <t xml:space="preserve">code</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -983,12 +969,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段名称</t>
+          <t xml:space="preserve">产业名称</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1010,44 +996,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段键</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_key</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业字段</t>
+          <t xml:space="preserve">产业类型</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段类型</t>
+          <t xml:space="preserve">图标</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">field_type</t>
+          <t xml:space="preserve">icon</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1064,17 +1045,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">默认值</t>
+          <t xml:space="preserve">所属产业</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">default_value</t>
+          <t xml:space="preserve">industry_type</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -1086,17 +1072,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否计算字段</t>
+          <t xml:space="preserve">字段名称</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">is_calculated</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">是/否</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -1108,17 +1099,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">计算图</t>
+          <t xml:space="preserve">字段键</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">graph</t>
+          <t xml:space="preserve">field_key</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSON 文本</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -1130,17 +1126,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">启用财年定时器</t>
+          <t xml:space="preserve">字段类型</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_enabled</t>
+          <t xml:space="preserve">field_type</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">是/否</t>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1148,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">定时器时机</t>
+          <t xml:space="preserve">默认值</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_trigger</t>
+          <t xml:space="preserve">default_value</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1174,17 +1170,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">定时器写入值</t>
+          <t xml:space="preserve">是否计算字段</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">timer_value</t>
+          <t xml:space="preserve">is_calculated</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">是/否</t>
         </is>
       </c>
     </row>
@@ -1196,17 +1192,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">排序</t>
+          <t xml:space="preserve">计算图</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">sort_order</t>
+          <t xml:space="preserve">graph</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">JSON 文本</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1214,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否展示</t>
+          <t xml:space="preserve">启用财年定时器</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">visible</t>
+          <t xml:space="preserve">timer_enabled</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1240,12 +1236,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型配置</t>
+          <t xml:space="preserve">定时器时机</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">config</t>
+          <t xml:space="preserve">timer_trigger</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1257,93 +1253,83 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称</t>
+          <t xml:space="preserve">定时器写入值</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">timer_value</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">排序</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">sort_order</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点类型</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型名称</t>
+          <t xml:space="preserve">是否展示</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">visible</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">是/否</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点类型</t>
+          <t xml:space="preserve">产业字段</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">类型配置</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">config</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1355,88 +1341,93 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点类型</t>
+          <t xml:space="preserve">区域</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">颜色</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">color</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">区域</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型名称</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">地图节点类型</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">地图节点类型</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">颜色</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">color</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1448,44 +1439,39 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点</t>
+          <t xml:space="preserve">地图节点类型</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点名称</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">color</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点类型</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">node_type</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1502,17 +1488,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属区域</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1524,22 +1510,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图节点</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">X坐标</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">x</t>
+          <t xml:space="preserve">color</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
     </row>
@@ -1551,34 +1537,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y坐标</t>
+          <t xml:space="preserve">节点名称</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">y</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图连线</t>
+          <t xml:space="preserve">地图节点</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">起点节点</t>
+          <t xml:space="preserve">节点类型</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_node</t>
+          <t xml:space="preserve">node_type</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1595,98 +1586,83 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图连线</t>
+          <t xml:space="preserve">地图节点</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">终点节点</t>
+          <t xml:space="preserve">所属区域</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_node</t>
+          <t xml:space="preserve">region</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图连线</t>
+          <t xml:space="preserve">地图节点</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">距离(公里)</t>
+          <t xml:space="preserve">X坐标</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">distance</t>
+          <t xml:space="preserve">x</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
           <t xml:space="preserve">数字（可按文本填写以保精度）</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">地图连线</t>
+          <t xml:space="preserve">地图节点</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">Y坐标</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">path_type</t>
+          <t xml:space="preserve">y</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">地图连线</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料名称</t>
+          <t xml:space="preserve">起点节点</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">from_node</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -1703,44 +1679,49 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">地图连线</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">每升单价</t>
+          <t xml:space="preserve">终点节点</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">price_per_liter</t>
+          <t xml:space="preserve">to_node</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料</t>
+          <t xml:space="preserve">地图连线</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料名称</t>
+          <t xml:space="preserve">距离(公里)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">distance</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -1752,66 +1733,76 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料</t>
+          <t xml:space="preserve">地图连线</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">产地</t>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">origin</t>
+          <t xml:space="preserve">path_type</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">碳排系数</t>
+          <t xml:space="preserve">燃料名称</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_emission_coefficient</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型</t>
+          <t xml:space="preserve">每升单价</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">price_per_liter</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
@@ -1823,61 +1814,61 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">地点价</t>
+          <t xml:space="preserve">原料名称</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">node_prices</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技</t>
+          <t xml:space="preserve">原料</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技名称</t>
+          <t xml:space="preserve">产地</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">origin</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技</t>
+          <t xml:space="preserve">原料</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">层级</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">carbon_emission_coefficient</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -1889,44 +1880,44 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技</t>
+          <t xml:space="preserve">原料</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">研发费用</t>
+          <t xml:space="preserve">类型</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">research_cost</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技</t>
+          <t xml:space="preserve">原料</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">地点价</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">node_prices</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
         </is>
       </c>
     </row>
@@ -1938,61 +1929,61 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">前置科技</t>
+          <t xml:space="preserve">科技名称</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">prerequisites</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线</t>
+          <t xml:space="preserve">科技</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线名称</t>
+          <t xml:space="preserve">层级</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">tier</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线</t>
+          <t xml:space="preserve">科技</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">研发费用</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">research_cost</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2004,56 +1995,56 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线</t>
+          <t xml:space="preserve">科技</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">用工人数</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">labor_count</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线</t>
+          <t xml:space="preserve">科技</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">年产能</t>
+          <t xml:space="preserve">前置科技</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_per_year</t>
+          <t xml:space="preserve">prerequisites</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">列表（分号分隔）</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建</t>
+          <t xml:space="preserve">生产线</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建名称</t>
+          <t xml:space="preserve">生产线名称</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2075,17 +2066,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建</t>
+          <t xml:space="preserve">生产线</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">占地面积</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">footprint</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2097,17 +2088,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建</t>
+          <t xml:space="preserve">生产线</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">用工人数</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">labor_count</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2119,17 +2110,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建</t>
+          <t xml:space="preserve">生产线</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">启用费用</t>
+          <t xml:space="preserve">年产能</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">activation_price</t>
+          <t xml:space="preserve">max_per_year</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2146,17 +2137,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">就业率加成</t>
+          <t xml:space="preserve">基建名称</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">employment_rate_bonus</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2164,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">人口加成</t>
+          <t xml:space="preserve">占地面积</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">population_bonus</t>
+          <t xml:space="preserve">footprint</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2190,12 +2186,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">高素质人口加成</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">high_quality_population_bonus</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2212,12 +2208,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">幸福度加成</t>
+          <t xml:space="preserve">启用费用</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">happiness_index_bonus</t>
+          <t xml:space="preserve">activation_price</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2234,12 +2230,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">人均收益加成</t>
+          <t xml:space="preserve">就业率加成</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">per_capita_income_bonus</t>
+          <t xml:space="preserve">employment_rate_bonus</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2256,12 +2252,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">减碳加成</t>
+          <t xml:space="preserve">人口加成</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_reduction_bonus</t>
+          <t xml:space="preserve">population_bonus</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2273,71 +2269,61 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库</t>
+          <t xml:space="preserve">基建</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库名称</t>
+          <t xml:space="preserve">高素质人口加成</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">high_quality_population_bonus</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库</t>
+          <t xml:space="preserve">基建</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库种类</t>
+          <t xml:space="preserve">幸福度加成</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">happiness_index_bonus</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库</t>
+          <t xml:space="preserve">基建</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">容量</t>
+          <t xml:space="preserve">人均收益加成</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacity</t>
+          <t xml:space="preserve">per_capita_income_bonus</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2349,17 +2335,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库</t>
+          <t xml:space="preserve">基建</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">减碳加成</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">carbon_reduction_bonus</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2371,12 +2357,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件</t>
+          <t xml:space="preserve">仓库</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件名称</t>
+          <t xml:space="preserve">仓库名称</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2398,159 +2384,159 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件</t>
+          <t xml:space="preserve">仓库</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料配比</t>
+          <t xml:space="preserve">仓库种类</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">materials</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件</t>
+          <t xml:space="preserve">仓库</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">所需科技</t>
+          <t xml:space="preserve">容量</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">tech</t>
+          <t xml:space="preserve">capacity</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品</t>
+          <t xml:space="preserve">仓库</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品名称</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品</t>
+          <t xml:space="preserve">零件</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件配比</t>
+          <t xml:space="preserve">零件名称</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">parts</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品</t>
+          <t xml:space="preserve">零件</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">所需科技</t>
+          <t xml:space="preserve">原料配比</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">tech</t>
+          <t xml:space="preserve">materials</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
+          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具</t>
+          <t xml:space="preserve">零件</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具名称</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">tech</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">列表（分号分隔）</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具</t>
+          <t xml:space="preserve">产品</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2567,44 +2553,44 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具</t>
+          <t xml:space="preserve">产品</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">可通行路径类型</t>
+          <t xml:space="preserve">零件配比</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">path_types</t>
+          <t xml:space="preserve">parts</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">列表（分号分隔）</t>
+          <t xml:space="preserve">键值（名称:数值，分号分隔）</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具</t>
+          <t xml:space="preserve">产品</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">每公里油耗</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel_consumption_per_km</t>
+          <t xml:space="preserve">tech</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">列表（分号分隔）</t>
         </is>
       </c>
     </row>
@@ -2616,17 +2602,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">载货量</t>
+          <t xml:space="preserve">载具名称</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_cargo</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2629,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">price</t>
+          <t xml:space="preserve">fuel</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -2660,137 +2656,122 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">碳排系数</t>
+          <t xml:space="preserve">可通行路径类型</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">carbon_emission</t>
+          <t xml:space="preserve">path_types</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+          <t xml:space="preserve">列表（分号分隔）</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费者需求</t>
+          <t xml:space="preserve">载具</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称</t>
+          <t xml:space="preserve">每公里油耗</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">fuel_consumption_per_km</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费者需求</t>
+          <t xml:space="preserve">载具</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品名称</t>
+          <t xml:space="preserve">载货量</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">product</t>
+          <t xml:space="preserve">max_cargo</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费者需求</t>
+          <t xml:space="preserve">载具</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">需求量</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantity</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
           <t xml:space="preserve">数字（可按文本填写以保精度）</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">消费者需求</t>
+          <t xml:space="preserve">载具</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">备注</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">carbon_emission</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">文本</t>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">合同类型</t>
+          <t xml:space="preserve">消费者需求</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">脚本路径</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">region</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -2807,42 +2788,145 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">合同类型</t>
+          <t xml:space="preserve">消费者需求</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型标识</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">product</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t xml:space="preserve">消费者需求</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">需求量</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quantity</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字（可按文本填写以保精度）</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">消费者需求</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">备注</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
           <t xml:space="preserve">合同类型</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">脚本路径</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">script</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">类型标识</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合同类型</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
         <is>
           <t xml:space="preserve">是否启用</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t xml:space="preserve">enabled</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t xml:space="preserve">是/否</t>
         </is>
@@ -2858,22 +2942,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">起点节点</t>
+          <t xml:space="preserve">节点名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">终点节点</t>
+          <t xml:space="preserve">节点类型</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">距离(公里)</t>
+          <t xml:space="preserve">所属区域</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">路径类型</t>
+          <t xml:space="preserve">X坐标</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y坐标</t>
         </is>
       </c>
     </row>
@@ -2885,23 +2974,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t xml:space="preserve">矿区</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上游资源区</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t xml:space="preserve">上游集运站</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公路</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物流枢纽</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上游资源区</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300</t>
+        </is>
+      </c>
+    </row>
     <row r="4"/>
     <row r="5"/>
+    <row r="6"/>
   </sheetData>
 </worksheet>
 </file>
@@ -2912,24 +3033,44 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料名称</t>
+          <t xml:space="preserve">起点节点</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">每升单价</t>
+          <t xml:space="preserve">终点节点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">距离(公里)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">路径类型</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">柴油</t>
+          <t xml:space="preserve">白云鄂博矿区</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.6</t>
+          <t xml:space="preserve">上游集运站</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公路</t>
         </is>
       </c>
     </row>
@@ -2946,54 +3087,24 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料名称</t>
+          <t xml:space="preserve">燃料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">产地</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">碳排系数</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">类型</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">地点价</t>
+          <t xml:space="preserve">每升单价</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">锂矿石</t>
+          <t xml:space="preserve">柴油</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">白云鄂博矿区</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.52</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NORMAL</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白云鄂博矿区:180; 上游集运站:195</t>
+          <t xml:space="preserve">7.6</t>
         </is>
       </c>
     </row>
@@ -3010,49 +3121,54 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">科技名称</t>
+          <t xml:space="preserve">原料名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">层级</t>
+          <t xml:space="preserve">产地</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">研发费用</t>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">类型</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">前置科技</t>
+          <t xml:space="preserve">地点价</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">电池成组技术</t>
+          <t xml:space="preserve">锂矿石</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">白云鄂博矿区</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80000</t>
+          <t xml:space="preserve">0.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">解锁动力电池包</t>
+          <t xml:space="preserve">NORMAL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白云鄂博矿区:180; 上游集运站:195</t>
         </is>
       </c>
     </row>
@@ -3069,44 +3185,49 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">生产线名称</t>
+          <t xml:space="preserve">科技名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">层级</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">用工人数</t>
+          <t xml:space="preserve">研发费用</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">年产能</t>
+          <t xml:space="preserve">说明</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前置科技</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">电芯产线</t>
+          <t xml:space="preserve">电池成组技术</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400000</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">80000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">解锁动力电池包</t>
         </is>
       </c>
     </row>
@@ -3123,84 +3244,44 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">基建名称</t>
+          <t xml:space="preserve">生产线名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">占地面积</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">用工人数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">启用费用</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">就业率加成</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">人口加成</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高素质人口加成</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">幸福度加成</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">人均收益加成</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">减碳加成</t>
+          <t xml:space="preserve">年产能</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">光伏电站</t>
+          <t xml:space="preserve">电芯产线</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160</t>
+          <t xml:space="preserve">2400000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200000</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.02</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.12</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
     </row>
@@ -3217,44 +3298,84 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库名称</t>
+          <t xml:space="preserve">基建名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">仓库种类</t>
+          <t xml:space="preserve">占地面积</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">容量</t>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">单价</t>
+          <t xml:space="preserve">启用费用</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">就业率加成</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人口加成</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高素质人口加成</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幸福度加成</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人均收益加成</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">减碳加成</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料仓</t>
+          <t xml:space="preserve">光伏电站</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATERIAL</t>
+          <t xml:space="preserve">160</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30000</t>
+          <t xml:space="preserve">1200000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">400000</t>
+          <t xml:space="preserve">50000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.02</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.12</t>
         </is>
       </c>
     </row>
@@ -3271,34 +3392,44 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件名称</t>
+          <t xml:space="preserve">仓库名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">原料配比</t>
+          <t xml:space="preserve">仓库种类</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所需科技</t>
+          <t xml:space="preserve">容量</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单价</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">动力电池包</t>
+          <t xml:space="preserve">原料仓</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">锂矿石*4; 铝土矿*1</t>
+          <t xml:space="preserve">MATERIAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">电池成组技术</t>
+          <t xml:space="preserve">30000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400000</t>
         </is>
       </c>
     </row>
@@ -3315,12 +3446,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品名称</t>
+          <t xml:space="preserve">零件名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">零件配比</t>
+          <t xml:space="preserve">原料配比</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -3332,17 +3463,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">纯电轿车</t>
+          <t xml:space="preserve">动力电池包</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">动力电池包*1; 驱动电机*1</t>
+          <t xml:space="preserve">锂矿石*4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">整车平台化</t>
+          <t xml:space="preserve">电池成组技术</t>
         </is>
       </c>
     </row>
@@ -3359,74 +3490,34 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">载具名称</t>
+          <t xml:space="preserve">产品名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃料</t>
+          <t xml:space="preserve">零件配比</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">可通行路径类型</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">每公里油耗</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">载货量</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">单价</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">碳排系数</t>
+          <t xml:space="preserve">所需科技</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">重型卡车</t>
+          <t xml:space="preserve">纯电轿车</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">柴油</t>
+          <t xml:space="preserve">动力电池包*1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.35</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.9</t>
+          <t xml:space="preserve">电池成组技术</t>
         </is>
       </c>
     </row>
@@ -3492,44 +3583,74 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称</t>
+          <t xml:space="preserve">载具名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">产品名称</t>
+          <t xml:space="preserve">燃料</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">需求量</t>
+          <t xml:space="preserve">可通行路径类型</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">备注</t>
+          <t xml:space="preserve">每公里油耗</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载货量</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单价</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碳排系数</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">东部车都</t>
+          <t xml:space="preserve">重型卡车</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">纯电轿车</t>
+          <t xml:space="preserve">柴油</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200</t>
+          <t xml:space="preserve">公路</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">城市通勤主力车型</t>
+          <t xml:space="preserve">0.35</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.9</t>
         </is>
       </c>
     </row>
@@ -3546,6 +3667,60 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">区域名称</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">产品名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">需求量</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东部车都</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">纯电轿车</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">城市通勤主力车型</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t xml:space="preserve">脚本路径</t>
         </is>
       </c>
@@ -3624,39 +3799,19 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">编码</t>
+          <t xml:space="preserve">参数</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">产业名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">图标</t>
+          <t xml:space="preserve">值</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">原料开采</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汽车产业链上游</t>
+          <t xml:space="preserve"># 留空 = 沿用系统默认；要改就按「参数 / 值」逐行填，参数名见规范（limitPct、maxMovePct、mmMinQty…）</t>
         </is>
       </c>
     </row>
@@ -3673,104 +3828,39 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属产业</t>
+          <t xml:space="preserve">编码</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段名称</t>
+          <t xml:space="preserve">产业名称</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段键</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段类型</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">默认值</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否计算字段</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">计算图</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">启用财年定时器</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定时器时机</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定时器写入值</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">排序</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是否展示</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">类型配置</t>
+          <t xml:space="preserve">图标</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">原料开采</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">现金</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cash</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NUMBER</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是</t>
+          <t xml:space="preserve">汽车产业链上游</t>
         </is>
       </c>
     </row>
@@ -3787,24 +3877,104 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">区域名称</t>
+          <t xml:space="preserve">所属产业</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t xml:space="preserve">字段名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字段键</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字段类型</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">默认值</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否计算字段</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">计算图</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">启用财年定时器</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定时器时机</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定时器写入值</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">排序</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是否展示</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">类型配置</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">上游资源区</t>
+          <t xml:space="preserve">原料开采</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">锂 / 铝 / 铁矿与橡胶硅砂资源带</t>
+          <t xml:space="preserve">现金</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cash</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NUMBER</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">是</t>
         </is>
       </c>
     </row>
@@ -3821,34 +3991,24 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型名称</t>
+          <t xml:space="preserve">区域名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
           <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">颜色</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿区</t>
+          <t xml:space="preserve">上游资源区</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">原矿开采地</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#b45309</t>
+          <t xml:space="preserve">锂 / 铝 / 铁矿与橡胶硅砂资源带</t>
         </is>
       </c>
     </row>
@@ -3882,23 +4042,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">公路</t>
+          <t xml:space="preserve">矿区</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">通用公路运输</t>
+          <t xml:space="preserve">原矿开采地</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#94a3b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t xml:space="preserve">#b45309</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物流枢纽</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">集运站 / 港口 / 铁路货场</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#0ea5e9</t>
+        </is>
+      </c>
+    </row>
     <row r="4"/>
     <row r="5"/>
+    <row r="6"/>
   </sheetData>
 </worksheet>
 </file>
@@ -3909,54 +4086,34 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点名称</t>
+          <t xml:space="preserve">类型名称</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">节点类型</t>
+          <t xml:space="preserve">说明</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">所属区域</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">X坐标</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y坐标</t>
+          <t xml:space="preserve">颜色</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">白云鄂博矿区</t>
+          <t xml:space="preserve">公路</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿区</t>
+          <t xml:space="preserve">通用公路运输</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">上游资源区</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">#94a3b8</t>
         </is>
       </c>
     </row>
